--- a/out/thesis/tables/create_vs_announcement_deal_level.xlsx
+++ b/out/thesis/tables/create_vs_announcement_deal_level.xlsx
@@ -1848,6 +1848,12 @@
       <c r="O2">
         <v>-0.0191463628305016</v>
       </c>
+      <c r="P2">
+        <v>0.0599726966423985</v>
+      </c>
+      <c r="Q2">
+        <v>0.0599726966423985</v>
+      </c>
       <c r="V2">
         <v>-0.0261015901858683</v>
       </c>
@@ -1936,6 +1942,12 @@
       <c r="O4">
         <v>0.0172982794017794</v>
       </c>
+      <c r="P4">
+        <v>-0.1049479214183662</v>
+      </c>
+      <c r="Q4">
+        <v>-0.1049479214183662</v>
+      </c>
       <c r="V4">
         <v>0.0906872901736578</v>
       </c>
@@ -2001,6 +2013,12 @@
       <c r="O5">
         <v>-0.0304188835725068</v>
       </c>
+      <c r="P5">
+        <v>0.0183288624593963</v>
+      </c>
+      <c r="Q5">
+        <v>0.0183288624593963</v>
+      </c>
       <c r="V5">
         <v>-0.0642415032336645</v>
       </c>
@@ -2066,6 +2084,12 @@
       <c r="O6">
         <v>-0.00035138617429</v>
       </c>
+      <c r="P6">
+        <v>-0.2200161620071082</v>
+      </c>
+      <c r="Q6">
+        <v>-0.2051592308366765</v>
+      </c>
       <c r="V6">
         <v>0.0198014373367231</v>
       </c>
@@ -2131,6 +2155,12 @@
       <c r="O7">
         <v>-0.0547599204248638</v>
       </c>
+      <c r="P7">
+        <v>0.0043284034701298</v>
+      </c>
+      <c r="Q7">
+        <v>0.0043284034701298</v>
+      </c>
       <c r="V7">
         <v>-0.0481421909835967</v>
       </c>
@@ -2196,6 +2226,12 @@
       <c r="O8">
         <v>0.0500278194622016</v>
       </c>
+      <c r="P8">
+        <v>0.0210058642654298</v>
+      </c>
+      <c r="Q8">
+        <v>0.0210058642654298</v>
+      </c>
       <c r="V8">
         <v>0.012121043267931</v>
       </c>
@@ -2261,6 +2297,12 @@
       <c r="O9">
         <v>0.2197523099509714</v>
       </c>
+      <c r="P9">
+        <v>-0.0524362063773464</v>
+      </c>
+      <c r="Q9">
+        <v>-0.0524362063773464</v>
+      </c>
       <c r="V9">
         <v>0.1692284405701283</v>
       </c>
@@ -2326,6 +2368,12 @@
       <c r="O10">
         <v>0.0448903134067721</v>
       </c>
+      <c r="P10">
+        <v>0.07831768959610851</v>
+      </c>
+      <c r="Q10">
+        <v>1.482897124560623E-05</v>
+      </c>
       <c r="V10">
         <v>-0.0379988006070108</v>
       </c>
@@ -2483,6 +2531,12 @@
       <c r="O15">
         <v>0.0015167836865462</v>
       </c>
+      <c r="P15">
+        <v>-0.1264073003440089</v>
+      </c>
+      <c r="Q15">
+        <v>-0.1264073003440089</v>
+      </c>
       <c r="V15">
         <v>0.1096160199391082</v>
       </c>
@@ -2548,6 +2602,12 @@
       <c r="O16">
         <v>-0.0300113082576603</v>
       </c>
+      <c r="P16">
+        <v>0.0528505149469764</v>
+      </c>
+      <c r="Q16">
+        <v>0.0528505149469764</v>
+      </c>
       <c r="V16">
         <v>-0.0822583223868953</v>
       </c>
@@ -2613,6 +2673,12 @@
       <c r="O17">
         <v>-0.0010636870978297</v>
       </c>
+      <c r="P17">
+        <v>0.1072876450822095</v>
+      </c>
+      <c r="Q17">
+        <v>0.1072876450822095</v>
+      </c>
       <c r="V17">
         <v>0.0314966708597088</v>
       </c>
@@ -2678,6 +2744,12 @@
       <c r="O18">
         <v>0.0860414371925962</v>
       </c>
+      <c r="P18">
+        <v>0.0322620630862957</v>
+      </c>
+      <c r="Q18">
+        <v>0.0322620630862957</v>
+      </c>
       <c r="V18">
         <v>-0.0196065414075698</v>
       </c>
@@ -2743,6 +2815,12 @@
       <c r="O19">
         <v>-0.08862750602300939</v>
       </c>
+      <c r="P19">
+        <v>-0.0627555359868322</v>
+      </c>
+      <c r="Q19">
+        <v>-0.0627555359868322</v>
+      </c>
       <c r="V19">
         <v>0.0216336537388328</v>
       </c>
@@ -2808,6 +2886,12 @@
       <c r="O20">
         <v>0.0056413249568522</v>
       </c>
+      <c r="P20">
+        <v>0.06839189492452249</v>
+      </c>
+      <c r="Q20">
+        <v>0.06839189492452249</v>
+      </c>
       <c r="V20">
         <v>0.031777896812287</v>
       </c>
@@ -2919,6 +3003,12 @@
       <c r="O23">
         <v>-0.019731137725047</v>
       </c>
+      <c r="P23">
+        <v>0.0388190436671485</v>
+      </c>
+      <c r="Q23">
+        <v>0.0701366718073963</v>
+      </c>
       <c r="V23">
         <v>-0.0280162997168469</v>
       </c>
@@ -2984,6 +3074,12 @@
       <c r="O24">
         <v>0.0442544600639148</v>
       </c>
+      <c r="P24">
+        <v>0.0118198184419636</v>
+      </c>
+      <c r="Q24">
+        <v>0.0137043589535125</v>
+      </c>
       <c r="V24">
         <v>-0.0397636432215742</v>
       </c>
@@ -3044,7 +3140,7 @@
         <v>0.0096762414914171</v>
       </c>
       <c r="N25">
-        <v>-0.025543668703464</v>
+        <v>0.0232093000063558</v>
       </c>
       <c r="O25">
         <v>0.0239489925871982</v>
@@ -3065,7 +3161,7 @@
         <v>0.0041001124552615</v>
       </c>
       <c r="AA25">
-        <v>0.0494926612906622</v>
+        <v>0.0007396925808423986</v>
       </c>
     </row>
     <row r="26" spans="1:27">
@@ -3114,6 +3210,12 @@
       <c r="O26">
         <v>0.0931077916061667</v>
       </c>
+      <c r="P26">
+        <v>-0.0205480346605203</v>
+      </c>
+      <c r="Q26">
+        <v>-0.0205480346605203</v>
+      </c>
       <c r="V26">
         <v>-0.0036879351010081</v>
       </c>
@@ -3179,6 +3281,12 @@
       <c r="O27">
         <v>-0.07507943508422631</v>
       </c>
+      <c r="P27">
+        <v>-0.0213850710005576</v>
+      </c>
+      <c r="Q27">
+        <v>-0.0213850710005576</v>
+      </c>
       <c r="V27">
         <v>0.053478952596707</v>
       </c>
@@ -3220,6 +3328,9 @@
       <c r="G28">
         <v>2578</v>
       </c>
+      <c r="P28">
+        <v>0.4382903435752072</v>
+      </c>
     </row>
     <row r="29" spans="1:27">
       <c r="A29">
@@ -3266,6 +3377,9 @@
       <c r="G30">
         <v>0</v>
       </c>
+      <c r="P30">
+        <v>0.4382903435752072</v>
+      </c>
     </row>
     <row r="31" spans="1:27">
       <c r="A31">
@@ -3359,6 +3473,12 @@
       <c r="O33">
         <v>0.0015167836865462</v>
       </c>
+      <c r="P33">
+        <v>-0.1264073003440089</v>
+      </c>
+      <c r="Q33">
+        <v>-0.1264073003440089</v>
+      </c>
       <c r="V33">
         <v>0.1096160199391082</v>
       </c>
@@ -3424,6 +3544,12 @@
       <c r="O34">
         <v>0.1301953400216202</v>
       </c>
+      <c r="P34">
+        <v>0.4296650309450538</v>
+      </c>
+      <c r="Q34">
+        <v>0.4296650309450538</v>
+      </c>
       <c r="V34">
         <v>0.1047564439083413</v>
       </c>
@@ -3489,6 +3615,12 @@
       <c r="O35">
         <v>-0.3796172008132212</v>
       </c>
+      <c r="P35">
+        <v>-0.433768397667315</v>
+      </c>
+      <c r="Q35">
+        <v>-0.433768397667315</v>
+      </c>
       <c r="V35">
         <v>-0.1455486493585274</v>
       </c>
@@ -3541,6 +3673,9 @@
       </c>
       <c r="N36">
         <v>0.0215732279846899</v>
+      </c>
+      <c r="P36">
+        <v>0.0069705366503109</v>
       </c>
       <c r="V36">
         <v>-0.0156176257942202</v>
